--- a/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
+++ b/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="81">
   <si>
     <t>普通测试的优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,6 +320,26 @@
   </si>
   <si>
     <t>12月底发版本，在发布版本前需要工程编译文档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗留sdbhelp chm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -331,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +368,14 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -384,7 +408,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -400,13 +424,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -782,10 +809,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="18.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>11</v>
@@ -794,89 +821,89 @@
         <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="7"/>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="6" t="s">
-        <v>25</v>
+      <c r="D5" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="6" t="s">
-        <v>20</v>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="7"/>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1">
@@ -885,239 +912,245 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" t="s">
         <v>33</v>
       </c>
-      <c r="G11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" t="s">
+      <c r="C34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" t="s">
         <v>45</v>
       </c>
-      <c r="E34" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" t="s">
+    </row>
+    <row r="36" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="18.75" customHeight="1">
@@ -1125,100 +1158,100 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
         <v>49</v>
       </c>
-      <c r="E38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="G43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A46" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A46" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="18.75" customHeight="1">
@@ -1226,76 +1259,106 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A51" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" t="s">
+        <v>50</v>
+      </c>
+      <c r="G51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A54" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A51" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" t="s">
-        <v>51</v>
-      </c>
-      <c r="G51" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A54" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
         <v>71</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" t="s">
         <v>72</v>
-      </c>
-      <c r="E54" t="s">
-        <v>74</v>
-      </c>
-      <c r="G54" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="C2:C9"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="B28:B32"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="A54:A55"/>
@@ -1305,36 +1368,6 @@
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="A51:A52"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="C2:C9"/>
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
+++ b/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
@@ -144,10 +144,6 @@
     <t>优先级可以放低</t>
   </si>
   <si>
-    <t>需要同时部署原生和修改后的pg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>工作量是按熟悉builder工具算的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -233,12 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>添加选项：break_on_failure
-用例执行前后检测环境
-多次执行用例，使用例稳定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>执行前启停节点
 用例执行前后检测环境
 多次执行用例，使用例稳定</t>
@@ -301,6 +291,17 @@
   <si>
     <t>是用旧的调度还是新的调度
 如何适配调度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加选项：break_on_failure
+用例执行前后检测环境
+多次执行用例，使用例稳定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要同时部署原生和修改后的pg
+梳理下原来的调度脚本</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -757,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -769,7 +770,7 @@
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>12</v>
@@ -780,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -800,36 +801,36 @@
         <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="47.25" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -843,13 +844,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -860,13 +861,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -878,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -898,13 +899,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
@@ -915,13 +916,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -935,7 +936,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -955,16 +956,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="33.75" hidden="1" customHeight="1">
@@ -972,13 +973,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
@@ -992,13 +993,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -1007,21 +1008,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="25.5" customHeight="1">
+    <row r="14" spans="1:7" ht="32.25" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="46.5" customHeight="1">
@@ -1029,53 +1030,53 @@
         <v>8</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="35.25" hidden="1" customHeight="1">
       <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
         <v>39</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32.25" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
+++ b/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="75" windowWidth="18750" windowHeight="8490"/>
+    <workbookView xWindow="360" yWindow="75" windowWidth="18720" windowHeight="8490"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="72">
   <si>
     <t>普通测试的优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,10 +38,6 @@
   </si>
   <si>
     <t>稳定性测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>代码覆盖率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -302,6 +298,41 @@
   <si>
     <t>需要同时部署原生和修改后的pg
 梳理下原来的调度脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码覆盖率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原生pg exit_on_error是关闭的，后续需要调整测试框架，然后打开参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -744,7 +775,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="18.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.5" customWidth="1"/>
@@ -753,347 +784,378 @@
     <col min="4" max="4" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="18.75" customHeight="1">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="63.75" hidden="1" customHeight="1">
+    </row>
+    <row r="2" spans="1:8" ht="63.75" hidden="1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32.25" hidden="1" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="47.25" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="32.25" hidden="1" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="47.25" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="47.25" customHeight="1">
+    </row>
+    <row r="5" spans="1:8" ht="47.25" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="34.5" hidden="1" customHeight="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="34.5" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="30.75" hidden="1" customHeight="1">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="30.75" hidden="1" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="78" customHeight="1">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="78" hidden="1" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.5" hidden="1" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="34.5" hidden="1" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="32.25" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="46.5" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="35.25" hidden="1" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="32.25" hidden="1" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" hidden="1" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="33.75" hidden="1" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="34.5" hidden="1" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="32.25" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="35.25" hidden="1" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
         <v>59</v>
       </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="32.25" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>60</v>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17">
+  <autoFilter ref="A1:H17">
     <filterColumn colId="1">
       <filters>
-        <filter val="高"/>
         <filter val="中"/>
       </filters>
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="挂起"/>
-        <filter val="启动中"/>
         <filter val="未开始"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="5"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
+++ b/internal_doc/ci_improve_plan/ci_imporve_plan.xlsx
@@ -774,7 +774,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="18.75" customHeight="1"/>
   <cols>
@@ -810,7 +809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="63.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="63.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -830,7 +829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="32.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="32.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -856,7 +855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="47.25" customHeight="1">
+    <row r="4" spans="1:8" ht="60.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -917,7 +916,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="30.75" hidden="1" customHeight="1">
+    <row r="7" spans="1:8" ht="30.75" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
@@ -937,7 +936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="78" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="78" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
@@ -1000,7 +999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="43.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="43.5" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -1017,7 +1016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="12" spans="1:8" ht="33.75" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>27</v>
       </c>
@@ -1037,7 +1036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="34.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:8" ht="34.5" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1097,7 +1096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="35.25" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="35.25" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="32.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:7" ht="32.25" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
@@ -1144,19 +1143,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="中"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="未开始"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5"/>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1167,6 +1153,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="3" width="9" customWidth="1"/>
+  </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
